--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -507,7 +507,7 @@
         <v>4.526479999999951</v>
       </c>
       <c r="D5">
-        <v>-0.2280799999999382</v>
+        <v>-0.2280799999999394</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -861,10 +861,10 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>6.105200000000003</v>
+        <v>6.105200000000004</v>
       </c>
       <c r="D26">
-        <v>-0.6077599999999693</v>
+        <v>-0.6077599999999682</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -1099,10 +1099,10 @@
         <v>14</v>
       </c>
       <c r="C40">
-        <v>5.273583577922919</v>
+        <v>5.27358357792292</v>
       </c>
       <c r="D40">
-        <v>-0.4535257593620557</v>
+        <v>-0.4535257593620523</v>
       </c>
       <c r="E40">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -861,10 +861,10 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>6.105200000000004</v>
+        <v>6.105200000000005</v>
       </c>
       <c r="D26">
-        <v>-0.6077599999999682</v>
+        <v>-0.6077599999999672</v>
       </c>
       <c r="E26">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.927364392626764</v>
+        <v>4.927364392626762</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579519</v>
+        <v>-0.6674744605579497</v>
       </c>
       <c r="E7">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.927364392626762</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579497</v>
+        <v>-0.6674744605579519</v>
       </c>
       <c r="E7">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -489,7 +489,7 @@
         <v>5.717839999999994</v>
       </c>
       <c r="D5">
-        <v>-0.7995999999999612</v>
+        <v>-0.7995999999999623</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.927364392626764</v>
+        <v>4.927364392626763</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579519</v>
+        <v>-0.6674744605579529</v>
       </c>
       <c r="E7">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -489,7 +489,7 @@
         <v>5.717839999999994</v>
       </c>
       <c r="D5">
-        <v>-0.7995999999999623</v>
+        <v>-0.7995999999999612</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.927364392626763</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579529</v>
+        <v>-0.6674744605579519</v>
       </c>
       <c r="E7">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -438,7 +438,7 @@
         <v>4.355919999999943</v>
       </c>
       <c r="D2">
-        <v>-0.387919999999945</v>
+        <v>-0.3879199999999439</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -486,10 +486,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>5.717839999999994</v>
+        <v>5.717839999999993</v>
       </c>
       <c r="D5">
-        <v>-0.7995999999999623</v>
+        <v>-0.7995999999999612</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.927364392626763</v>
+        <v>4.92736439262676</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579529</v>
+        <v>-0.6674744605579497</v>
       </c>
       <c r="E7">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -486,10 +486,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>5.717839999999993</v>
+        <v>5.717839999999994</v>
       </c>
       <c r="D5">
-        <v>-0.7995999999999612</v>
+        <v>-0.7995999999999646</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.92736439262676</v>
+        <v>4.927364392626761</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579497</v>
+        <v>-0.6674744605579508</v>
       </c>
       <c r="E7">
         <v>5</v>

--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -438,7 +438,7 @@
         <v>4.355919999999943</v>
       </c>
       <c r="D2">
-        <v>-0.3879199999999439</v>
+        <v>-0.387919999999945</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -489,7 +489,7 @@
         <v>5.717839999999994</v>
       </c>
       <c r="D5">
-        <v>-0.7995999999999646</v>
+        <v>-0.7995999999999612</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -520,10 +520,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4.927364392626761</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="D7">
-        <v>-0.6674744605579508</v>
+        <v>-0.6674744605579519</v>
       </c>
       <c r="E7">
         <v>5</v>
